--- a/productos_import_masivo_modelo.xlsx
+++ b/productos_import_masivo_modelo.xlsx
@@ -9,8 +9,8 @@
 <cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-02-27T18:12:17Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-02-27T18:12:17Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-03T23:16:49Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-03T23:16:49Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -68,32 +68,32 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>codigoExterno</t>
+          <t>categoriaNombre</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>categoriaNombre</t>
+          <t>colorNombre</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>colorNombre</t>
+          <t>colorHex</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>colorHex</t>
+          <t>tallaNombre</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>tallaNombre</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>precioOferta</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -125,31 +125,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EXT-POL-001-NEG-M</t>
+          <t>Poleras</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Poleras</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Negro</t>
+          <t>#111111</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>#111111</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>M</t>
         </is>
       </c>
+      <c r="H2">
+        <v>49.9</v>
+      </c>
       <c r="I2">
-        <v>49.9</v>
+        <v>39.9</v>
       </c>
       <c r="J2">
         <v>20</v>
@@ -178,31 +176,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EXT-POL-001-NEG-L</t>
+          <t>Poleras</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Poleras</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negro</t>
+          <t>#111111</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>#111111</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>L</t>
         </is>
       </c>
+      <c r="H3">
+        <v>49.9</v>
+      </c>
       <c r="I3">
-        <v>49.9</v>
+        <v>39.9</v>
       </c>
       <c r="J3">
         <v>18</v>
@@ -231,31 +227,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EXT-POL-001-BLA-M</t>
+          <t>Poleras</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Poleras</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>#FFFFFF</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>49.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J4">
         <v>15</v>
@@ -284,31 +280,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EXT-POL-001-BLA-L</t>
+          <t>Poleras</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Poleras</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>#FFFFFF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5">
+      <c r="H5">
         <v>49.9</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J5">
         <v>12</v>
@@ -337,31 +333,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EXT-JOG-010-GRI-M</t>
+          <t>Pantalones</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pantalones</t>
+          <t>Gris</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gris</t>
+          <t>#808080</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>#808080</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
           <t>M</t>
         </is>
       </c>
+      <c r="H6">
+        <v>89</v>
+      </c>
       <c r="I6">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -390,31 +384,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EXT-JOG-010-GRI-L</t>
+          <t>Pantalones</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pantalones</t>
+          <t>Gris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gris</t>
+          <t>#808080</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>#808080</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
           <t>L</t>
         </is>
       </c>
+      <c r="H7">
+        <v>89</v>
+      </c>
       <c r="I7">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -443,31 +435,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EXT-JOG-010-AZU-M</t>
+          <t>Pantalones</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pantalones</t>
+          <t>Azul Marino</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Azul Marino</t>
+          <t>#1B2A49</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>#1B2A49</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I8">
+      <c r="H8">
         <v>92</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J8">
         <v>8</v>
@@ -496,31 +488,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EXT-CAM-022-CRE-M</t>
+          <t>Camisas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Camisas</t>
+          <t>Crema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Crema</t>
+          <t>#F5F5DC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>#F5F5DC</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
           <t>M</t>
         </is>
       </c>
+      <c r="H9">
+        <v>129.5</v>
+      </c>
       <c r="I9">
-        <v>129.5</v>
+        <v>114.5</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -549,31 +539,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EXT-CAM-022-CRE-L</t>
+          <t>Camisas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Camisas</t>
+          <t>Crema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crema</t>
+          <t>#F5F5DC</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>#F5F5DC</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
           <t>L</t>
         </is>
       </c>
+      <c r="H10">
+        <v>129.5</v>
+      </c>
       <c r="I10">
-        <v>129.5</v>
+        <v>114.5</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -602,31 +590,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EXT-CAM-022-MUS-M</t>
+          <t>Camisas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Camisas</t>
+          <t>Verde Musgo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Verde Musgo</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I11">
+      <c r="H11">
         <v>132</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J11">
         <v>5</v>
